--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -13090,7 +13090,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -13120,7 +13120,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -13150,7 +13150,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -13180,7 +13180,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -13210,7 +13210,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -13240,7 +13240,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -13270,7 +13270,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -13300,7 +13300,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -13330,7 +13330,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -13360,7 +13360,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -13390,7 +13390,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -13420,7 +13420,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -13450,7 +13450,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -13480,7 +13480,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -13510,7 +13510,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -13540,7 +13540,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -13570,7 +13570,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -13630,7 +13630,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -13660,7 +13660,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -13720,7 +13720,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13750,7 +13750,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -13780,7 +13780,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -13840,7 +13840,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -13870,7 +13870,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -13900,7 +13900,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -13930,7 +13930,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -13960,7 +13960,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -13990,7 +13990,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -14020,7 +14020,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14050,7 +14050,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -14080,7 +14080,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -14110,7 +14110,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -14140,7 +14140,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -14200,7 +14200,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -14230,7 +14230,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -14260,7 +14260,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -14290,7 +14290,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -14320,7 +14320,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -14350,7 +14350,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -14380,7 +14380,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -14410,7 +14410,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -14440,7 +14440,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -14470,7 +14470,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -14500,7 +14500,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -14530,7 +14530,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -14560,7 +14560,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -14590,7 +14590,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -14620,7 +14620,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -14650,7 +14650,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -14710,7 +14710,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -14740,7 +14740,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -14770,7 +14770,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -14800,7 +14800,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14830,7 +14830,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14860,7 +14860,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14890,7 +14890,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14920,7 +14920,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14950,7 +14950,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -14980,7 +14980,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15010,7 +15010,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15040,7 +15040,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">

--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -13037,21 +13037,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cycle 2 plan. First pass = the full day. Cadence revisit / Producer sweep = the producing accounts only (2–4 quick stops). Pick the weekday at the Monday huddle.</t>
+          <t>5 route-day slots per week. First pass = the full day. Cadence revisit = the producers due on rhythm, packed into one full loop day (a label like R03+R07 = one drive covering both days’ producers). Open slots are flex. Pick weekdays at the Monday huddle.</t>
         </is>
       </c>
     </row>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Route Day</t>
+          <t>Route Day(s)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>K-R05</t>
         </is>
@@ -13128,7 +13128,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>K-R08</t>
         </is>
@@ -13158,7 +13158,7 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>K-R09</t>
         </is>
@@ -13188,22 +13188,22 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>K-R13</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>K-R11</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Producer sweep</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates</t>
+          <t>Lupo Chiropractic Center · Legacy Family Medicine · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center · Corewell Health-East</t>
         </is>
       </c>
     </row>
@@ -13218,22 +13218,22 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>K-R15</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>K-R12</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Producer sweep</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
+          <t>Neil King Physical Therapy · Troy Internal Medicine · Clawson Internists · MedPro Primary Care · Oakland Family Practice · Sterling Family Medicine · Metro Medical Practice · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
         </is>
       </c>
     </row>
@@ -13248,9 +13248,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>K-R02</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>K-R02+R06</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -13259,11 +13259,11 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Hesselberg Chiropractic · Park Medical Centers</t>
+          <t>Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · Hesselberg Chiropractic · Park Medical Centers</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>K-R03</t>
         </is>
@@ -13308,22 +13308,22 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>K-R06</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>K-R13</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law</t>
+          <t>Blue Water Internal Medicine PC · Internal Medicine Associates Port Huron · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Physician HeathCare Network - Michele Raymond DO · Port Huron Medicine Associates · Patrick Kut MD PC</t>
         </is>
       </c>
     </row>
@@ -13338,9 +13338,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>K-R11</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>K-R14</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -13349,11 +13349,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Lupo Chiropractic Center · Legacy Family Medicine · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center · Corewell Health-East</t>
+          <t>Haller and Hug Internal Medicine · WILLIAMS FAMILY AND SPORTS MEDICAL CENTER, PLC · TONI BALLITCH TRATE, DO, PC · Trinity IHA Primary Care - Schoolcraft Campus · Medical Clinic of Northville · Village Medical - Northville West · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · Providence Park Pediatrics - Novi · WELL BEING PEDIATRICS · Ivy Rehab - Novi</t>
         </is>
       </c>
     </row>
@@ -13368,9 +13368,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>K-R12</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>K-R15</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Neil King Physical Therapy · Troy Internal Medicine · Clawson Internists · MedPro Primary Care · Oakland Family Practice · Sterling Family Medicine · Metro Medical Practice · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
+          <t>WESTERN WAYNE PHYSICIANS, PLC Allen Park · ALLEN PARK FAMILY PHYSICIANS · Corewell Urgent Care - Allen Park · Premier Pediatrics Dearborn Heights · ARBOR LANE FAMILY PHYSICIANS · Corewell Health Urgent Care - Garden City · GARDEN CITY FAMILY PHYSICIANS · BEAUMONT FAMILY MEDICINE WESTLAND · Greg Monroe DO PC · WESTLAND CLINIC - use</t>
         </is>
       </c>
     </row>
@@ -13398,9 +13398,9 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>K-R17</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>K-R18</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Swetech Medical Center · MNP · Team Rehabilitation  - Washington</t>
+          <t>Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>K-R01</t>
         </is>
@@ -13458,9 +13458,9 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>K-R02</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>K-R02+R10</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -13469,11 +13469,11 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC</t>
+          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
         </is>
       </c>
     </row>
@@ -13488,9 +13488,9 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>K-R03</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>K-R03+R06+R07</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -13499,11 +13499,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
+          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
         </is>
       </c>
     </row>
@@ -13518,7 +13518,7 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>K-R04</t>
         </is>
@@ -13548,39 +13548,39 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>K-R06</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>K-R17</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC</t>
+          <t>Physician HeathCare Network - Marysville · Henry Ford Orthopedics &amp; Sports Medicine - Chesterfield · Physician HealthCare Network · Swetech Medical Center · Macomb Spine Care · Silver Pine Medical Group - Sterling Heights · Cornerstone St. Clair Internists · MNP · Souva PT and Performance · Team Rehabilitation  - Washington</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>K-R07</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>K-R01+R05+R07</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -13589,28 +13589,28 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE</t>
+          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>K-R10</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>K-R04+R08</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -13619,41 +13619,41 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
+          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road · IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>K-R16</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>K-R09+R10</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Producer sweep</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic</t>
+          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
         </is>
       </c>
     </row>
@@ -13668,9 +13668,9 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>K-R01</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>K-R11+R12</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -13679,11 +13679,11 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East · MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
         </is>
       </c>
     </row>
@@ -13698,39 +13698,39 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>K-R04</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>K-R16</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010</t>
+          <t>Wadhams Family Care · Blue Water Urgent Care - Port Huron · Dr. Carley and Associates · Lake Huron Medical Center - Fort Gratiot · Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · McLaren Port Huron Fort Gratiot Internal Medicine · Lexington Family Medicine · Croswell Clinic - McKenzie Health System · Yale Family Care · Yale Community Heath Center - VA Clinic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>K-R05</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>K-R02+R08+R13</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -13739,28 +13739,28 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Hesselberg Chiropractic · Park Medical Centers · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>K-R07</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>K-R03+R05+R06</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -13769,28 +13769,28 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law</t>
+          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · Internal Medicine Physicians #170 · Berry Johnson Health · Corwell Health - Farmington</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>K-R08</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>K-R03+R15</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -13799,28 +13799,28 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
+          <t>ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC · Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>K-R09</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>K-R09+R14</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -13829,28 +13829,28 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
+          <t>WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180 · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>K-R10</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>K-R11+R12</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -13859,33 +13859,33 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
+          <t>Legacy Family Medicine · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center · Neil King Physical Therapy · Troy Internal Medicine · Sterling Family Medicine · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>K-R14</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>K-R01+R04</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -13893,24 +13893,24 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Haller and Hug Internal Medicine · WILLIAMS FAMILY AND SPORTS MEDICAL CENTER, PLC · TONI BALLITCH TRATE, DO, PC · Trinity IHA Primary Care - Schoolcraft Campus · Medical Clinic of Northville · Village Medical - Northville West · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · Providence Park Pediatrics - Novi · WELL BEING PEDIATRICS · Ivy Rehab - Novi</t>
+          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford · Commerce Internal Medicine · Oakland Physicians</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>K-R02</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>K-R04+R10</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -13919,28 +13919,28 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Hesselberg Chiropractic · Park Medical Centers</t>
+          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>K-R03</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>K-R07+R13</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -13949,28 +13949,28 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Corewell Internal Medicine Southfield · Corwell Health - Farmington · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
+          <t>Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · SOUTH EAST MICHIGAN MEDICAL ASSOCIATES, PC · MEDICAL CENTER PEDIATRICS, PLLC · Blue Water Internal Medicine PC · Internal Medicine Associates Port Huron · Physician HeathCare Network - Michele Raymond DO · Patrick Kut MD PC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>K-R05</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>K-R10+R14</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -13979,28 +13979,28 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one</t>
+          <t>SOMERSET PEDIATRICS · Rochester Primary Care · Haller and Hug Internal Medicine · Trinity IHA Primary Care - Schoolcraft Campus · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · WELL BEING PEDIATRICS · Ivy Rehab - Novi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>K-R06</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>K-R15+R17</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -14009,28 +14009,28 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Levine Clinic of Chiropractic · Internal Medicine Physicians #170 · Jian Zu MD · Berry Johnson Health · Carson Center Specialty · Ross Law</t>
+          <t>Swetech Medical Center · MNP · Team Rehabilitation  - Washington · ALLEN PARK FAMILY PHYSICIANS · Corewell Urgent Care - Allen Park · Premier Pediatrics Dearborn Heights · Corewell Health Urgent Care - Garden City · BEAUMONT FAMILY MEDICINE WESTLAND · WESTLAND CLINIC - use</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>K-R08</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>K-R02+R03</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -14039,28 +14039,28 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine</t>
+          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>K-R09</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>K-R05+R06</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -14069,28 +14069,28 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
+          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Corewell Urgent Care - Royal Oak · Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>K-R11</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>K-R08+R09</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -14099,28 +14099,28 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East</t>
+          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>K-R12</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>K-R11+R12</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -14129,28 +14129,28 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
+          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East · MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>K-R01</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>K-R16+R17</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -14159,28 +14159,28 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
+          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic · Physician HeathCare Network - Marysville · Physician HealthCare Network · Silver Pine Medical Group - Sterling Heights · Cornerstone St. Clair Internists · Souva PT and Performance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>K-R04</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>K-R01+R13+R15</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -14189,28 +14189,28 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>DMC Orthopedics - Commerce Township · Commerce Internal Medicine · CoreMed - Commerce · Oakland Physicians · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD</t>
+          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>K-R07</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>K-R02+R06+R07+R15</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -14219,28 +14219,28 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Applebaum &amp; Stone · SOUTH EAST MICHIGAN MEDICAL ASSOCIATES, PC · Wigod &amp; Falzon · MEDICAL CENTER PEDIATRICS, PLLC · Steinberg Law Firm · ROSE MEDICINE</t>
+          <t>Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Hesselberg Chiropractic · Park Medical Centers · WESTERN WAYNE PHYSICIANS, PLC Allen Park</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>K-R10</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>K-R03+R14</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -14249,28 +14249,28 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Victor Valentino Law · SOMERSET PEDIATRICS · TWIN LAKES MEDICAL ASSOCIATES, PC · Rochester Primary Care · Stonebrooke Family Physicians</t>
+          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington · WILLIAMS FAMILY AND SPORTS MEDICAL CENTER, PLC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>K-R11</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>K-R04+R09+R16</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -14279,28 +14279,28 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Legacy Family Medicine · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center</t>
+          <t>Wadhams Family Care · Blue Water Urgent Care - Port Huron · Dr. Carley and Associates · Lake Huron Medical Center - Fort Gratiot · McLaren Port Huron Fort Gratiot Internal Medicine · Croswell Clinic - McKenzie Health System · IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010 · Internal Medicine Specialists · Associates in Internal Medicine - MHP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>K-R12</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>K-R10+R14</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -14309,28 +14309,28 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Neil King Physical Therapy · Troy Internal Medicine · Sterling Family Medicine · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
+          <t>Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>K-R02</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>K-R01</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -14339,28 +14339,28 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC</t>
+          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>K-R03</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>K-R04+R10</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -14369,28 +14369,28 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
+          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>K-R05</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>K-R05+R07+R11</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -14399,28 +14399,28 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Lifetime Family Care · Corewell Urgent Care - Royal Oak · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Legacy Family Medicine · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>K-R06</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>K-R08+R09+R17</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -14429,28 +14429,28 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC</t>
+          <t>Henry Ford Orthopedics &amp; Sports Medicine - Chesterfield · Macomb Spine Care · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>K-R08</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>K-R12+R17</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -14459,611 +14459,11 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>K-R09</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Internal Medicine Specialists · Center For Hollistic Medicine · Associates in Internal Medicine - MHP · MARY LEE, MD, PC · Vanstone Injury Law</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>K-R14</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>K-R18</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>K-R01</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>K-R02</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Hesselberg Chiropractic · Park Medical Centers</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>K-R03</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>K-R04</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>K-R06</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>K-R07</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>K-R10</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>K-R11</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>K-R12</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>K-R01</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>K-R04</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>K-R05</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>K-R07</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>K-R08</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>K-R09</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>K-R10</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>K-R14</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Haller and Hug Internal Medicine · Trinity IHA Primary Care - Schoolcraft Campus · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · WELL BEING PEDIATRICS · Ivy Rehab - Novi</t>
+          <t>Neil King Physical Therapy · Troy Internal Medicine · Sterling Family Medicine · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one · Swetech Medical Center · MNP · Team Rehabilitation  - Washington</t>
         </is>
       </c>
     </row>

--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kristen — Spine Route Days v2 · validated universe (your eyeball pass, Jul 31) · “No” accounts removed · cadence: T1 21d · T2 30d · T3/prospect 45d</t>
+          <t>Kristen — Spine Route Days v2 · validated universe (eyeball pass, Jul 31) · “No” accounts removed · cadence: T1 21d · T2 30d · T3/prospect 45d  ||  MERGED Jul 31: Sean’s 40 accounts are now yours — days K-R19 to K-R22 (Warren / Sterling Heights / Clinton Twp / St. Clair Shores). Your original day numbers did not change.</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>Backlog (Oct+ / after 90-day read)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1372,6 +1372,186 @@
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Warren (9) • Sterling Heights (1)</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>intact (Day 02) · reassigned from Sean</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Heights (4) • Troy (2) • South Lyon (1)</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>intact (Day 03) · reassigned from Sean</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Heights (6) • Clinton Township (2) • Macomb Township (1)</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>intact (Day 01) · reassigned from Sean</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>St. Clair Shores (3) • Roseville (2) • Saint Clair Shores (2)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>intact (Day 04) · reassigned from Sean</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Backlog (Oct+ / after 90-day read)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Open in Maps</t>
         </is>
@@ -1400,6 +1580,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1411,7 +1595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N177"/>
+  <dimension ref="A1:N217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13023,6 +13207,2642 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>c88f05f1-5992-43b0-947c-469a44a0feef</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Ryan Medical Associates</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>Repeat Spine Referrer</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L178" s="7" t="inlineStr">
+        <is>
+          <t>21647 Ryan Rd, Warren, MI, 48091</t>
+        </is>
+      </c>
+      <c r="M178" s="7" t="inlineStr">
+        <is>
+          <t>Kevin A Agrest, DO (1 spine) · Christine England, NP (1 spine) · Jeffrey A Kraft, DO (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N178" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>476bc8e4-84c4-4063-97a9-b649ed44dddf</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Horizon Care Medical Group - Warren</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>26000 Hoover Rd #103, Warren, Michigan, 48089</t>
+        </is>
+      </c>
+      <c r="M179" s="7" t="inlineStr">
+        <is>
+          <t>Anthony Spearman, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N179" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>8ae19fc3-b1ab-4f35-ab71-b73d93833918</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care - Warren</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>26000 Hoover Rd, Warren, Michigan, 48089</t>
+        </is>
+      </c>
+      <c r="M180" s="7" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care Warren (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N180" s="6" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>1750481842</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Medical Associates - Warren</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>27540 Hoover Rd, Warren, MI, 480934505</t>
+        </is>
+      </c>
+      <c r="M181" s="7" t="inlineStr">
+        <is>
+          <t>Srinivas Koneru (1 ortho) · Robert Marcotte (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N181" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>33d0c0aa-7d47-450d-9673-71acb651321c</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>Michigan Compassionate Care</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>Repeat Spine Referrer</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>28401 Hoover, Warren, Michigan, 48093</t>
+        </is>
+      </c>
+      <c r="M182" s="7" t="inlineStr">
+        <is>
+          <t>Muhammad Vasiq, MD (2 spine) · Michigan Compassionate Care (2 ortho)</t>
+        </is>
+      </c>
+      <c r="N182" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>1700860103</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>Michigan Adult and Child Medicine</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>11885 E. 12 Mile Rd, Ste 100A, Warren, Michigan, 48093</t>
+        </is>
+      </c>
+      <c r="M183" s="7" t="inlineStr">
+        <is>
+          <t>Renee Y Paye, MD (2 ortho) · John Byrne, MD (1 ortho) · Jeffrey Fisher, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N183" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>954353cc-a941-4b77-90f3-f3fb1c62e161</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>DIAB AND KINNER INTERNAL MEDICINE, PC- use</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t>WARREN</t>
+        </is>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>29703 HOOVER RD STE A, WARREN, Michigan, 48093</t>
+        </is>
+      </c>
+      <c r="M184" s="7" t="inlineStr">
+        <is>
+          <t>Carolann Kinner, DO (1 spine)</t>
+        </is>
+      </c>
+      <c r="N184" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>6aee51ce-625f-4968-96c5-5d9a6936bf27</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>MI Family Practice</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Repeat Spine Referrer</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J185" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L185" s="7" t="inlineStr">
+        <is>
+          <t>11300 E 13 Mile Rd, Suite 1, Warren, MI, 48093</t>
+        </is>
+      </c>
+      <c r="M185" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Garza, DO (2 spine) · Taras Lisowsky, DO (1 spine)</t>
+        </is>
+      </c>
+      <c r="N185" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>1932273448</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>Henry Ford Medical Center - Warren</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>Visit / Prospect</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>8600 Chicago Road St, Warren, MI, 48093</t>
+        </is>
+      </c>
+      <c r="M186" s="7" t="inlineStr"/>
+      <c r="N186" s="6" t="inlineStr">
+        <is>
+          <t>Mixed panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>K-R19</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>1bcc2e23-5fc1-428c-ad41-dc35c5345bf7</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care - Sterling Heights</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>2567 Metro Parkway, Sterling Heights, Michigan, 48310</t>
+        </is>
+      </c>
+      <c r="M187" s="7" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care Of Sterling Heights (1 spine) · Get Well Urgent Care - Sterling Heights (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N187" s="6" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>573750f7-b7bd-4246-b7ac-f1217823639f</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>South Lyon Family Docs</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>South Lyon</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>26006 Pontiac Trail, South Lyon, MI, 48178</t>
+        </is>
+      </c>
+      <c r="M188" s="4" t="inlineStr">
+        <is>
+          <t>Brandy Eberhardt, DO (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>1774d7c7-2d8b-42c6-9dac-78c2a9cf3ed8</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Berkley Urgent Care</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>Berkley</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>3270 Greenfield Rd, Berkley, Michigan, 48072</t>
+        </is>
+      </c>
+      <c r="M189" s="4" t="inlineStr">
+        <is>
+          <t>Berkley Urgent Care (1 spine)</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>1992798961</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>Downriver Internists</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>Oak Park</t>
+        </is>
+      </c>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>13801 W 9 Mile Rd, Oak Park, MI, 48237</t>
+        </is>
+      </c>
+      <c r="M190" s="4" t="inlineStr">
+        <is>
+          <t>Srinivas Gatla, MD (2 ortho)</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>346a1335-a97f-4a1a-9847-77f9e71383c3</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care Madison Heights</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Spine Referrer</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>Madison Heights</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>350 E 12 Mile Rd, Madison Heights, Michigan, 48071</t>
+        </is>
+      </c>
+      <c r="M191" s="4" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care - Madison Heights (1 spine) · Getwell Urgent Care- Madison Heights (1 spine)</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>3b700a13-2f3b-4e83-bd1f-61bd1cca19e6</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>Elite Family Medicine</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L192" s="4" t="inlineStr">
+        <is>
+          <t>33200 Dequindre Rd, Sterling Heights, Michigan, 48310</t>
+        </is>
+      </c>
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>Maha Hasso, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>0b9485b1-39bd-4f21-8222-387834af8472</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>Kashat Urgent care</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>35200 Dequindre Road, Sterling Heights, Michigan, 48310</t>
+        </is>
+      </c>
+      <c r="M193" s="4" t="inlineStr">
+        <is>
+          <t>Ghazawan K Kashat, MD (1 spine)</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>1972593499</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Physicians</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>36040 Dequindre Road, Sterling Heights, Michigan, 48310</t>
+        </is>
+      </c>
+      <c r="M194" s="4" t="inlineStr">
+        <is>
+          <t>James Burtka, MD (1 spine)</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>1386634749</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>Tri-County Medical Clinic</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>37450 DeQuindre Rd, Sterling Heights, MI, 48310</t>
+        </is>
+      </c>
+      <c r="M195" s="4" t="inlineStr">
+        <is>
+          <t>Kenneth J Wolok Do (1 spine) · Jeffrey S Deitch, DO (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>ea9682a6-09ea-4d32-a71d-171ffffb7847</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>Wattles Internal Medicine- use</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="inlineStr">
+        <is>
+          <t>1950 E Wattles Rd suite 101, Troy, Michigan, 48085</t>
+        </is>
+      </c>
+      <c r="M196" s="4" t="inlineStr">
+        <is>
+          <t>Mark Zohoury, DO (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>K-R20</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>63bf16ad-3645-45fb-8f1d-e1eb3a131efc</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Brigid Healthcare</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>Repeat Spine Referrer</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>3456 Rochester Rd, Troy, Michigan, 48083</t>
+        </is>
+      </c>
+      <c r="M197" s="4" t="inlineStr">
+        <is>
+          <t>Hui Wang, PA (2 spine)</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>d1255d1a-17e8-4765-bfe5-45c6c087c8ed</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>Toma &amp; Yaldo Medical Center</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>39150 Dequindre Rd suite 200, Sterling Heights, Michigan, 48310</t>
+        </is>
+      </c>
+      <c r="M198" s="7" t="inlineStr">
+        <is>
+          <t>Raad Toma, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N198" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>ce3b56cf-1381-41d0-b067-752448464958</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>Michigan Primary Care - Sterling Heights</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>41400 Dequindre Rd, ste 121, Sterling Heights, Michigan, 48314</t>
+        </is>
+      </c>
+      <c r="M199" s="7" t="inlineStr">
+        <is>
+          <t>Aleksandra Tasevski, NP (1 spine)</t>
+        </is>
+      </c>
+      <c r="N199" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>1952519001</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>Beaumont Family Medicine - Sterling Heights</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>Other Patient Referrer</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>44250 Dequindre, Sterling Heights, MI, 483141002</t>
+        </is>
+      </c>
+      <c r="M200" s="7" t="inlineStr">
+        <is>
+          <t>Hany Eraqi, MD</t>
+        </is>
+      </c>
+      <c r="N200" s="6" t="inlineStr">
+        <is>
+          <t>Mixed panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>1205856432</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Associates in Family Practice</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>42755 Mound Rd, Sterling Heights, Michigan, 48314</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="inlineStr">
+        <is>
+          <t>Fadi Oska, MD (1 spine)</t>
+        </is>
+      </c>
+      <c r="N201" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>719fbbb9-0131-4ed6-bfd7-14646d9c41fb</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Sterling Heights Urgent Care</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L202" s="7" t="inlineStr">
+        <is>
+          <t>37771 Schoenherr Rd Suite 102, Sterling Heights, MI 48312, United States, Sterling Heights, Michigan, 48312</t>
+        </is>
+      </c>
+      <c r="M202" s="7" t="inlineStr">
+        <is>
+          <t>Sterling Heights Urgent Care (2 ortho)</t>
+        </is>
+      </c>
+      <c r="N202" s="6" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>62e680e9-a222-400d-9186-a369d13cf23f</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Schoenherr Parkway Family Practice</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>13951 Plumbrook, Sterling Heights, Michigan, 48312</t>
+        </is>
+      </c>
+      <c r="M203" s="7" t="inlineStr">
+        <is>
+          <t>Mona Khater, MD (1 spine)</t>
+        </is>
+      </c>
+      <c r="N203" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>5271bbd8-dfe5-4d54-a0a2-f5547050cafe</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>Macomb Internal Medicine</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>Repeat Spine Referrer</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J204" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>Clinton Township</t>
+        </is>
+      </c>
+      <c r="L204" s="7" t="inlineStr">
+        <is>
+          <t>15520 19 Mile Road, Suite 480, Clinton Township, MI, 48038</t>
+        </is>
+      </c>
+      <c r="M204" s="7" t="inlineStr">
+        <is>
+          <t>Anu Duvoor, MD (2 spine) · Linda Kosal, DO (2 spine)</t>
+        </is>
+      </c>
+      <c r="N204" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>ec2dcadc-ce63-4324-aea0-52ae2b2bdd91</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>David S Weingarden MD &amp; Associates</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Orthopedic</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>Clinton Township</t>
+        </is>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>43555 Dalcoma Dr suite 4 Clinton Twp, Clinton Township, Michigan, 48038</t>
+        </is>
+      </c>
+      <c r="M205" s="7" t="inlineStr">
+        <is>
+          <t>David Davis, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N205" s="6" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>da57adc9-a2cf-4705-886d-76146cbbde06</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>Office of David Mandy DO</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>Pediatrics</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>Macomb Township</t>
+        </is>
+      </c>
+      <c r="L206" s="7" t="inlineStr">
+        <is>
+          <t>46600 Romeo Plank, Ste. 4, Macomb Township, MI, 48044</t>
+        </is>
+      </c>
+      <c r="M206" s="7" t="inlineStr">
+        <is>
+          <t>David Mandy (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N206" s="6" t="inlineStr">
+        <is>
+          <t>Peds — low fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>K-R21</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>97ae4125-fd10-47de-8cae-c053e42232d0</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>Academic Internal Medicine (Ascension)</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>Other Patient Referrer</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>57850 Van Dyke Ave ste 600, Washington, Michigan, 48094</t>
+        </is>
+      </c>
+      <c r="M207" s="7" t="inlineStr">
+        <is>
+          <t>Zain Kulairi, MD</t>
+        </is>
+      </c>
+      <c r="N207" s="6" t="inlineStr">
+        <is>
+          <t>Mixed panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>1427049683</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>MyCare Health Center - Mt Clemens</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>Mount Clemens</t>
+        </is>
+      </c>
+      <c r="L208" s="4" t="inlineStr">
+        <is>
+          <t>18 Market Street, ste C, Mount Clemens, MI, 48043</t>
+        </is>
+      </c>
+      <c r="M208" s="4" t="inlineStr">
+        <is>
+          <t>Christine M Allor Fnp-c (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
+          <t>MEDICAID? VERIFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>e73f759b-87dc-444f-a504-b954ddeeace1</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Masonic Medical Center - Ascension</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>St. Clair Shores</t>
+        </is>
+      </c>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>21099 Masonic, St. Clair Shores, Michigan, 48082</t>
+        </is>
+      </c>
+      <c r="M209" s="4" t="inlineStr">
+        <is>
+          <t>Jeanette Elizabeth Wilson, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
+          <t>Mixed panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>1780671461</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>Aquino Integrative Internal Medicine</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>Roseville</t>
+        </is>
+      </c>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>30695 Little Mack Avenue, ste 500, Roseville, Michigan, 48066</t>
+        </is>
+      </c>
+      <c r="M210" s="4" t="inlineStr">
+        <is>
+          <t>Robert Aquino, DO (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>16c0ac85-6d3c-4c74-97b4-385a2a7fac00</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>Cornerstone Lakefront Internists</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>St. Clair Shores</t>
+        </is>
+      </c>
+      <c r="L211" s="4" t="inlineStr">
+        <is>
+          <t>20952 Twelve Mile Rd ste 101, St. Clair Shores, Michigan, 48081</t>
+        </is>
+      </c>
+      <c r="M211" s="4" t="inlineStr">
+        <is>
+          <t>Benjamin Osowa, MD (1 spine)</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>8c04fb31-3380-488f-aa8a-954ff32146f2</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>Epic Health - St Clair Shores</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>St. Clair Shores</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>28001 Harper, St. Clair Shores, Michigan, 48081</t>
+        </is>
+      </c>
+      <c r="M212" s="4" t="inlineStr">
+        <is>
+          <t>Ronald Barnett, DO (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>1043384555</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>Henry Ford Medical Center - East Jefferson</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>One Spine Patient</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>Saint Clair Shores</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>24725 E Jefferson, Saint Clair Shores, MI, 48080</t>
+        </is>
+      </c>
+      <c r="M213" s="4" t="inlineStr">
+        <is>
+          <t>Eshel Turk, MD (1 spine)</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
+          <t>Mixed panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>1164469821</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>Waypointe Internal Medicine</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>Saint Clair Shores</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>24400 Greater Mack Ave, Saint Clair Shores, MI, 48080</t>
+        </is>
+      </c>
+      <c r="M214" s="4" t="inlineStr">
+        <is>
+          <t>Sara Ann Fox, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>1063423176</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>Allied Internists</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>Roseville</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>18263 E 10 Mile Rd, ste E, Roseville, Michigan, 48066</t>
+        </is>
+      </c>
+      <c r="M215" s="4" t="inlineStr">
+        <is>
+          <t>Wahed Ishaqsei, MD (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>c96dc780-a933-4f9f-aaa3-e1da22d0f35e</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>Roseville Family Practice</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>28295 Schoenherr Road Suite C, Warren, Michigan, 48088</t>
+        </is>
+      </c>
+      <c r="M216" s="4" t="inlineStr">
+        <is>
+          <t>Mark Holowinski, MD (2 ortho)</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
+          <t>Comm/Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>K-R22</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>f30f611c-772a-406a-9d92-231790b785c2</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Medical Center &amp; Urgent Care</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Urgent Care</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>Ortho Referrer</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>STERLING HEIGHTS</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>13409 E 14 MILE RD, STERLING HEIGHTS, Michigan, 48312</t>
+        </is>
+      </c>
+      <c r="M217" s="4" t="inlineStr">
+        <is>
+          <t>Mohammed Nader Bazzy (1 ortho)</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
+          <t>Mixed walk-in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
@@ -13037,7 +15857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -13100,12 +15920,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>K-R05</t>
+          <t>K-R11+R12</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -13113,7 +15933,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Lifetime Family Care · Corewell Urgent Care - Royal Oak · Ross Gilders Law · Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East · MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
         </is>
       </c>
     </row>
@@ -13130,12 +15950,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>K-R08</t>
+          <t>K-R13+R16</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -13143,7 +15963,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>BETTER HEALTH CLINIC · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · Hermann Banks MD PC · iTest Health Family Medicine · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
+          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic</t>
         </is>
       </c>
     </row>
@@ -13160,20 +15980,20 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>K-R09</t>
+          <t>K-R14+R18</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Internal Medicine Specialists · MARY LEE, MD, PC · Associates in Internal Medicine - MHP · Vanstone Injury Law · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
+          <t>Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
         </is>
       </c>
     </row>
@@ -13190,20 +16010,20 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>K-R11</t>
+          <t>K-R15+R17+R22</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Lupo Chiropractic Center · Legacy Family Medicine · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center · Corewell Health-East</t>
+          <t>Swetech Medical Center · MNP · Team Rehabilitation  - Washington · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
         </is>
       </c>
     </row>
@@ -13220,7 +16040,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>K-R12</t>
+          <t>K-R19</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -13233,7 +16053,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Neil King Physical Therapy · Troy Internal Medicine · Clawson Internists · MedPro Primary Care · Oakland Family Practice · Sterling Family Medicine · Metro Medical Practice · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
+          <t>Ryan Medical Associates · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Compassionate Care · Michigan Adult and Child Medicine · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Henry Ford Medical Center - Warren · Get Well Urgent Care - Sterling Heights</t>
         </is>
       </c>
     </row>
@@ -13310,7 +16130,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>K-R13</t>
+          <t>K-R05</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -13323,7 +16143,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Blue Water Internal Medicine PC · Internal Medicine Associates Port Huron · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Physician HeathCare Network - Michele Raymond DO · Port Huron Medicine Associates · Patrick Kut MD PC</t>
+          <t>Lifetime Family Care · Corewell Urgent Care - Royal Oak · Ross Gilders Law · Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
         </is>
       </c>
     </row>
@@ -13340,7 +16160,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>K-R14</t>
+          <t>K-R08</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -13349,11 +16169,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Haller and Hug Internal Medicine · WILLIAMS FAMILY AND SPORTS MEDICAL CENTER, PLC · TONI BALLITCH TRATE, DO, PC · Trinity IHA Primary Care - Schoolcraft Campus · Medical Clinic of Northville · Village Medical - Northville West · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · Providence Park Pediatrics - Novi · WELL BEING PEDIATRICS · Ivy Rehab - Novi</t>
+          <t>BETTER HEALTH CLINIC · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · Hermann Banks MD PC · iTest Health Family Medicine · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
         </is>
       </c>
     </row>
@@ -13370,7 +16190,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>K-R15</t>
+          <t>K-R20</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -13383,37 +16203,37 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>WESTERN WAYNE PHYSICIANS, PLC Allen Park · ALLEN PARK FAMILY PHYSICIANS · Corewell Urgent Care - Allen Park · Premier Pediatrics Dearborn Heights · ARBOR LANE FAMILY PHYSICIANS · Corewell Health Urgent Care - Garden City · GARDEN CITY FAMILY PHYSICIANS · BEAUMONT FAMILY MEDICINE WESTLAND · Greg Monroe DO PC · WESTLAND CLINIC - use</t>
+          <t>South Lyon Family Docs · Berkley Urgent Care · Downriver Internists · Get Well Urgent Care Madison Heights · Elite Family Medicine · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Wattles Internal Medicine- use · Brigid Healthcare</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>K-R18</t>
+          <t>K-R01</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Producer sweep</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC</t>
+          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
         </is>
       </c>
     </row>
@@ -13430,7 +16250,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>K-R01</t>
+          <t>K-R02+R10</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -13439,11 +16259,11 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
+          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
         </is>
       </c>
     </row>
@@ -13460,7 +16280,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>K-R02+R10</t>
+          <t>K-R03+R06+R07</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -13473,7 +16293,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
+          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
         </is>
       </c>
     </row>
@@ -13490,7 +16310,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>K-R03+R06+R07</t>
+          <t>K-R04</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -13499,11 +16319,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
+          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD</t>
         </is>
       </c>
     </row>
@@ -13520,42 +16340,42 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>K-R04</t>
+          <t>K-R09</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD</t>
+          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Internal Medicine Specialists · MARY LEE, MD, PC · Associates in Internal Medicine - MHP · Vanstone Injury Law · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>K-R17</t>
+          <t>K-R01+R18+R19</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -13563,7 +16383,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Physician HeathCare Network - Marysville · Henry Ford Orthopedics &amp; Sports Medicine - Chesterfield · Physician HealthCare Network · Swetech Medical Center · Macomb Spine Care · Silver Pine Medical Group - Sterling Heights · Cornerstone St. Clair Internists · MNP · Souva PT and Performance · Team Rehabilitation  - Washington</t>
+          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights · Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
     </row>
@@ -13580,7 +16400,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>K-R01+R05+R07</t>
+          <t>K-R04+R10</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -13589,11 +16409,11 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+          <t>IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010 · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
         </is>
       </c>
     </row>
@@ -13610,7 +16430,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>K-R04+R08</t>
+          <t>K-R07+R11</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -13619,11 +16439,11 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road · IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010</t>
+          <t>CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East</t>
         </is>
       </c>
     </row>
@@ -13640,20 +16460,20 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>K-R09+R10</t>
+          <t>K-R12+R13+R22</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
+          <t>MedPro Primary Care · Oakland Family Practice · Metro Medical Practice · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
         </is>
       </c>
     </row>
@@ -13670,50 +16490,50 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>K-R11+R12</t>
+          <t>K-R15+R16+R17</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East · MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
+          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic · Swetech Medical Center · MNP · Team Rehabilitation  - Washington · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>K-R16</t>
+          <t>K-R02+R06+R19</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>First pass</t>
+          <t>Cadence revisit</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Wadhams Family Care · Blue Water Urgent Care - Port Huron · Dr. Carley and Associates · Lake Huron Medical Center - Fort Gratiot · Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · McLaren Port Huron Fort Gratiot Internal Medicine · Lexington Family Medicine · Croswell Clinic - McKenzie Health System · Yale Family Care · Yale Community Heath Center - VA Clinic</t>
+          <t>Internal Medicine Physicians #170 · Berry Johnson Health · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine · Hesselberg Chiropractic · Park Medical Centers</t>
         </is>
       </c>
     </row>
@@ -13730,7 +16550,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>K-R02+R08+R13</t>
+          <t>K-R03</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -13739,11 +16559,11 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Hesselberg Chiropractic · Park Medical Centers · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine</t>
+          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
         </is>
       </c>
     </row>
@@ -13773,7 +16593,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · Internal Medicine Physicians #170 · Berry Johnson Health · Corwell Health - Farmington</t>
+          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · Corwell Health - Farmington</t>
         </is>
       </c>
     </row>
@@ -13790,7 +16610,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>K-R03+R15</t>
+          <t>K-R08</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -13799,11 +16619,11 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC · Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
+          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
         </is>
       </c>
     </row>
@@ -13820,7 +16640,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>K-R09+R14</t>
+          <t>K-R14+R20</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -13829,28 +16649,28 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180 · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
+          <t>Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>K-R11+R12</t>
+          <t>K-R01+R10</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -13859,11 +16679,11 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Legacy Family Medicine · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center · Neil King Physical Therapy · Troy Internal Medicine · Sterling Family Medicine · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
+          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford · SOMERSET PEDIATRICS · Rochester Primary Care</t>
         </is>
       </c>
     </row>
@@ -13880,7 +16700,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>K-R01+R04</t>
+          <t>K-R04+R08+R20</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -13889,11 +16709,11 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford · Commerce Internal Medicine · Oakland Physicians</t>
+          <t>South Lyon Family Docs · Downriver Internists · Elite Family Medicine · Wattles Internal Medicine- use · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine · Commerce Internal Medicine · Oakland Physicians</t>
         </is>
       </c>
     </row>
@@ -13910,7 +16730,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>K-R04+R10</t>
+          <t>K-R04+R09</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -13919,11 +16739,11 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
+          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
         </is>
       </c>
     </row>
@@ -13940,7 +16760,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>K-R07+R13</t>
+          <t>K-R05+R07</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -13949,11 +16769,11 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · SOUTH EAST MICHIGAN MEDICAL ASSOCIATES, PC · MEDICAL CENTER PEDIATRICS, PLLC · Blue Water Internal Medicine PC · Internal Medicine Associates Port Huron · Physician HeathCare Network - Michele Raymond DO · Patrick Kut MD PC</t>
+          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · SOUTH EAST MICHIGAN MEDICAL ASSOCIATES, PC · MEDICAL CENTER PEDIATRICS, PLLC</t>
         </is>
       </c>
     </row>
@@ -13970,7 +16790,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>K-R10+R14</t>
+          <t>K-R10</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -13979,28 +16799,28 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>SOMERSET PEDIATRICS · Rochester Primary Care · Haller and Hug Internal Medicine · Trinity IHA Primary Care - Schoolcraft Campus · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · WELL BEING PEDIATRICS · Ivy Rehab - Novi</t>
+          <t>Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>K-R15+R17</t>
+          <t>K-R02</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -14009,11 +16829,11 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Swetech Medical Center · MNP · Team Rehabilitation  - Washington · ALLEN PARK FAMILY PHYSICIANS · Corewell Urgent Care - Allen Park · Premier Pediatrics Dearborn Heights · Corewell Health Urgent Care - Garden City · BEAUMONT FAMILY MEDICINE WESTLAND · WESTLAND CLINIC - use</t>
+          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC</t>
         </is>
       </c>
     </row>
@@ -14030,7 +16850,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>K-R02+R03</t>
+          <t>K-R03+R18+R19</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -14039,11 +16859,11 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
+          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights · Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
         </is>
       </c>
     </row>
@@ -14060,7 +16880,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>K-R05+R06</t>
+          <t>K-R06+R11</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -14073,7 +16893,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Corewell Urgent Care - Royal Oak · Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC</t>
+          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC · Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East</t>
         </is>
       </c>
     </row>
@@ -14090,20 +16910,20 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>K-R08+R09</t>
+          <t>K-R12+R13+R22</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
+          <t>MedPro Primary Care · Oakland Family Practice · Metro Medical Practice · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
         </is>
       </c>
     </row>
@@ -14120,37 +16940,37 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>K-R11+R12</t>
+          <t>K-R15+R16+R17</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>Producer sweep</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East · MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
+          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic · Swetech Medical Center · MNP · Team Rehabilitation  - Washington · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>K-R16+R17</t>
+          <t>K-R01+R02+R08</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -14163,7 +16983,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic · Physician HeathCare Network - Marysville · Physician HealthCare Network · Silver Pine Medical Group - Sterling Heights · Cornerstone St. Clair Internists · Souva PT and Performance</t>
+          <t>Hesselberg Chiropractic · Park Medical Centers · Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
         </is>
       </c>
     </row>
@@ -14180,7 +17000,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>K-R01+R13+R15</t>
+          <t>K-R03+R04</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -14189,11 +17009,11 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington · IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010</t>
         </is>
       </c>
     </row>
@@ -14210,7 +17030,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>K-R02+R06+R07+R15</t>
+          <t>K-R05+R06</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -14223,7 +17043,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Hesselberg Chiropractic · Park Medical Centers · WESTERN WAYNE PHYSICIANS, PLC Allen Park</t>
+          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Corewell Urgent Care - Royal Oak · Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law</t>
         </is>
       </c>
     </row>
@@ -14240,7 +17060,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>K-R03+R14</t>
+          <t>K-R07+R20</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -14249,11 +17069,11 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington · WILLIAMS FAMILY AND SPORTS MEDICAL CENTER, PLC</t>
+          <t>CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare</t>
         </is>
       </c>
     </row>
@@ -14270,7 +17090,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>K-R04+R09+R16</t>
+          <t>K-R09+R10</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -14279,28 +17099,28 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Wadhams Family Care · Blue Water Urgent Care - Port Huron · Dr. Carley and Associates · Lake Huron Medical Center - Fort Gratiot · McLaren Port Huron Fort Gratiot Internal Medicine · Croswell Clinic - McKenzie Health System · IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010 · Internal Medicine Specialists · Associates in Internal Medicine - MHP</t>
+          <t>WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180 · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>K-R10+R14</t>
+          <t>K-R01</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -14309,11 +17129,11 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
+          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
         </is>
       </c>
     </row>
@@ -14330,7 +17150,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>K-R01</t>
+          <t>K-R04+R09</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -14339,11 +17159,11 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
+          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
         </is>
       </c>
     </row>
@@ -14360,7 +17180,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>K-R04+R10</t>
+          <t>K-R07+R09+R19</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -14369,11 +17189,11 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
+          <t>Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine · Internal Medicine Specialists · Associates in Internal Medicine - MHP</t>
         </is>
       </c>
     </row>
@@ -14390,7 +17210,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>K-R05+R07+R11</t>
+          <t>K-R10+R14</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -14399,11 +17219,11 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Legacy Family Medicine · METROPOLITAN MEDICAL ASSOCIATES · Health Care Medical Center</t>
+          <t>Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
         </is>
       </c>
     </row>
@@ -14420,50 +17240,20 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>K-R08+R09+R17</t>
+          <t>K-R21</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Cadence revisit</t>
+          <t>First pass</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Henry Ford Orthopedics &amp; Sports Medicine - Chesterfield · Macomb Spine Care · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>K-R12+R17</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Neil King Physical Therapy · Troy Internal Medicine · Sterling Family Medicine · Purdy Chiropractic Center · Plumbrook Medical Center · BASEL BRIKHO MEDICAL GROUP - use this one · Swetech Medical Center · MNP · Team Rehabilitation  - Washington</t>
+          <t>Toma &amp; Yaldo Medical Center · Michigan Primary Care - Sterling Heights · Beaumont Family Medicine - Sterling Heights · Associates in Family Practice · Sterling Heights Urgent Care · Schoenherr Parkway Family Practice · Macomb Internal Medicine · David S Weingarden MD &amp; Associates · Office of David Mandy DO · Academic Internal Medicine (Ascension)</t>
         </is>
       </c>
     </row>

--- a/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Kristen.xlsx
@@ -92,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,7 +509,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kristen — Spine Route Days v2 · validated universe (eyeball pass, Jul 31) · “No” accounts removed · cadence: T1 21d · T2 30d · T3/prospect 45d  ||  MERGED Jul 31: Sean’s 40 accounts are now yours — days K-R19 to K-R22 (Warren / Sterling Heights / Clinton Twp / St. Clair Shores). Your original day numbers did not change.</t>
+          <t>Kristen — HOME ROUTE DAYS (your territory reference, 22 days). These are the geographic clusters your accounts belong to — the days you actually drive are on the Weekly Plan tab. Validated universe (eyeball pass, Jul 31); cadence T1 21d · T2 30d · T3/prospect 45d.  ||  MERGED Jul 31: Sean’s 40 accounts are now yours — days K-R19 to K-R22 (Warren / Sterling Heights / Clinton Twp / St. Clair Shores). Your original day numbers did not change.</t>
         </is>
       </c>
     </row>
@@ -603,7 +606,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -648,7 +651,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -693,7 +696,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -738,7 +741,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -783,7 +786,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -828,7 +831,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -873,7 +876,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -918,7 +921,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -963,7 +966,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1008,7 +1011,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1053,7 +1056,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1098,7 +1101,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1143,7 +1146,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1188,7 +1191,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1233,7 +1236,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1278,7 +1281,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1323,7 +1326,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1368,7 +1371,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1458,7 +1461,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1503,7 +1506,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1548,7 +1551,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Backlog (Oct+ / after 90-day read)</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -15857,21 +15860,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="68" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 route-day slots per week. First pass = the full day. Cadence revisit = the producers due on rhythm, packed into one full loop day (a label like R03+R07 = one drive covering both days’ producers). Open slots are flex. Pick weekdays at the Monday huddle.</t>
+          <t>ONE ROW = ONE DAY YOU DRIVE. Day K-W1D1 means week 1, day 1 — the Stops column is the whole day, nothing to add up. Each day is built from whoever is due that week in one area (Tier 1 every 21 days · Tier 2 30 · Tier 3 45), with prospects from the same area riding along to fill it. “From home days” points back to the Route Days tab. Pick the weekday at the Monday huddle.</t>
         </is>
       </c>
     </row>
@@ -15888,172 +15897,312 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Route Day(s)</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Visit Kind</t>
+          <t>Stops</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Stops</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Who you’ll see</t>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Prospects</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Primary Area</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>From home days</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Navigate</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Who you’ll see (in order)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>K-R11+R12</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East · MedPro Primary Care · Oakland Family Practice · Metro Medical Practice</t>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>K-W1D1</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Warren (9) • Sterling Heights (1)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Medical Associates - Warren · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Ryan Medical Associates · DIAB AND KINNER INTERNAL MEDICINE, PC- use · Michigan Compassionate Care · Michigan Adult and Child Medicine · MI Family Practice · Henry Ford Medical Center - Warren · Get Well Urgent Care - Sterling Heights</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>K-R13+R16</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic</t>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>K-W1D2</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Sterling Heights (4) • Troy (2) • Madison Heights (1)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care Madison Heights · Berkley Urgent Care · Brigid Healthcare · Wattles Internal Medicine- use · South Lyon Family Docs · Downriver Internists · Elite Family Medicine · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>K-R14+R18</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>K-W1D3</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Southfield (6) • Royal Oak (2) • Warren (1)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>R05, R12</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>DEIGHTON FAMILY PRACTICE - use this one · Corewell Urgent Care - Royal Oak · Ross Gilders Law · Pavilion Family Practice - use this one · Superior Family Medicine - Health Venters Detroit -use this onea · APH - Pavillion IM Use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Sterling Family Medicine · Plumbrook Medical Center</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>K-R15+R17+R22</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Swetech Medical Center · MNP · Team Rehabilitation  - Washington · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>K-W1D4</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Sterling Heights (6) • Clinton Township (2) • Macomb Township (1)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Beaumont Family Medicine - Sterling Heights · Macomb Internal Medicine · David S Weingarden MD &amp; Associates · Office of David Mandy DO · Academic Internal Medicine (Ascension) · Toma &amp; Yaldo Medical Center · Sterling Heights Urgent Care · Schoenherr Parkway Family Practice · Michigan Primary Care - Sterling Heights · Associates in Family Practice</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>K-R19</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>K-W1D5</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Ryan Medical Associates · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Compassionate Care · Michigan Adult and Child Medicine · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Henry Ford Medical Center - Warren · Get Well Urgent Care - Sterling Heights</t>
+      <c r="E7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Livonia (8) • Redford (1) • Westland (1)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>R08, R15</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Henry Ford Health Medical Center - Seven Mile Road · ARBOR LANE FAMILY PHYSICIANS · Primal Recovery and PT · Brentwood Pediatric Associates · Village Medical - Livonia · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Dr. Robin’s Heath and Wellness Center · Hermann Banks MD PC · iTest Health Family Medicine · BETTER HEALTH CLINIC</t>
         </is>
       </c>
     </row>
@@ -16068,22 +16217,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>K-R02+R06</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>K-W2D1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · Hesselberg Chiropractic · Park Medical Centers</t>
+      <c r="F8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Warren (6) • Center Line (1) • Roseville (1)</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>R11, R12</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>FERRIS, MARY C, MEDICAL GROUP · Health Care Medical Center · Lupo Chiropractic Center · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · Corewell Health-East · METROPOLITAN MEDICAL ASSOCIATES · Henry Ford Warren Family Physicians · Troy Internal Medicine · Legacy Family Medicine</t>
         </is>
       </c>
     </row>
@@ -16098,22 +16269,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>K-R03</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>K-W2D2</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Clinton Township (2) • Marysville (1) • New Baltimore (1)</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Swetech Medical Center · Macomb Spine Care · Physician HeathCare Network - Marysville · Henry Ford Orthopedics &amp; Sports Medicine - Chesterfield · Physician HealthCare Network · Team Rehabilitation  - Washington · Silver Pine Medical Group - Sterling Heights · Cornerstone St. Clair Internists · Souva PT and Performance · MNP</t>
         </is>
       </c>
     </row>
@@ -16128,22 +16321,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>K-R05</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>K-W2D3</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Lifetime Family Care · Corewell Urgent Care - Royal Oak · Ross Gilders Law · Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
+        <v>6</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Port Huron (8) • Marysville (1) • Fort Gratiot Township (1)</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>R13, R16</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Port Huron Medicine Associates · Patrick Kut MD PC · Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Blue Water Internal Medicine PC · Internal Medicine Associates Port Huron · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Physician HeathCare Network - Michele Raymond DO</t>
         </is>
       </c>
     </row>
@@ -16158,22 +16373,44 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>K-R08</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>K-W2D4</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>BETTER HEALTH CLINIC · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · Hermann Banks MD PC · iTest Health Family Medicine · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Grosse Pointe (6) • Hamtramck (2) • Detroit (1)</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>FAMILY CARE CENTER OF HAMTRAMCK, PC · Hamtramck Community Medical Center · Marko Law · Henry Ford  SAINT CLAIR ADULT MEDICINE SPECIALISTS · GROSSE POINTE PARK INTERNAL MEDICINE CENTER · Grosse Pointe Physicians and Surgeons · Corewell Family Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · Henry Ford Main Internal Medicine - Grosse Pointe</t>
         </is>
       </c>
     </row>
@@ -16188,172 +16425,304 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>K-R20</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>K-W2D5</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>West Bloomfield (5) • Farmington Hills (3) • West Bloomfield Township (1)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>R09</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Center For Hollistic Medicine · Associates in Internal Medicine - MHP · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · MARY LEE, MD, PC · Internal Medicine Specialists · Vanstone Injury Law · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180 · Millenium Associated Physicians - 130A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K-W3D1</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>South Lyon Family Docs · Berkley Urgent Care · Downriver Internists · Get Well Urgent Care Madison Heights · Elite Family Medicine · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Wattles Internal Medicine- use · Brigid Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Novi (4) • Farmington Hills (2) • Northville (2)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>TONI BALLITCH TRATE, DO, PC · Providence Park Pediatrics - Novi · WELL BEING PEDIATRICS · Trinity IHA Primary Care - Schoolcraft Campus · Medical Clinic of Northville · Village Medical - Northville West · Haller and Hug Internal Medicine · WILLIAMS FAMILY AND SPORTS MEDICAL CENTER, PLC · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · Ivy Rehab - Novi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>K-R01</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K-W3D2</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Fort Gratiot (2) • Port Huron (2) • Yale (2)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>R05, R16</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Lake Huron Medical Center - Fort Gratiot · McLaren Port Huron Fort Gratiot Internal Medicine · Blue Water Urgent Care - Port Huron · Dr. Carley and Associates · Lifetime Family Care · Wadhams Family Care · Yale Family Care · Yale Community Heath Center - VA Clinic · Croswell Clinic - McKenzie Health System · Lexington Family Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K-W3D3</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>St. Clair Shores (3) • Roseville (2) • Saint Clair Shores (2)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>MyCare Health Center - Mt Clemens · Aquino Integrative Internal Medicine · Allied Internists · Henry Ford Medical Center - East Jefferson · Waypointe Internal Medicine · Cornerstone Lakefront Internists · Epic Health - St Clair Shores · Masonic Medical Center - Ascension · Roseville Family Practice · Sterling Medical Center &amp; Urgent Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>K-R02+R10</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K-W3D4</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC · Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="E16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Westland (3) • Allen Park (3) • Garden City (2)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>R02, R15</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>BEAUMONT FAMILY MEDICINE WESTLAND · WESTERN WAYNE PHYSICIANS, PLC Allen Park · ALLEN PARK FAMILY PHYSICIANS · Corewell Urgent Care - Allen Park · Premier Pediatrics Dearborn Heights · GARDEN CITY FAMILY PHYSICIANS · Corewell Health Urgent Care - Garden City · WESTLAND CLINIC - use · Greg Monroe DO PC · Hesselberg Chiropractic</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>K-R03+R06+R07</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K-W3D5</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>K-R04</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
+      <c r="E17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>K-R09</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Internal Medicine Specialists · MARY LEE, MD, PC · Associates in Internal Medicine - MHP · Vanstone Injury Law · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180</t>
+      <c r="F17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Rochester Hills (2) • Sterling Heights (2) • Clawson (1)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>R10, R12</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Clawson Internists · MedPro Primary Care · Metro Medical Practice · Oakland Family Practice · TWIN LAKES MEDICAL ASSOCIATES, PC · Victor Valentino Law · Neil King Physical Therapy · Stonebrooke Family Physicians · Purdy Chiropractic Center · BASEL BRIKHO MEDICAL GROUP - use this one</t>
         </is>
       </c>
     </row>
@@ -16368,22 +16737,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>K-R01+R18+R19</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>K-W4D1</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights · Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Farmington Hills (3) • Southfield (2) • Livonia (2)</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Corewell Health Farmington Hills Hospital Family Medicine · Christensen Law · Mike Morse Law Firm · Henry Ford Health - Family Medicine 8 Mile Livonia · Triumph chiropractic · Beaumont Medical Center - Redford · SHEIKH MEDICAL CENTER · Village Medical Farmington · Legacy Family Care · Powers Family Medicine</t>
         </is>
       </c>
     </row>
@@ -16398,22 +16789,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>K-R04+R10</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>K-W4D2</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010 · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
+        <v>10</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Warren (4) • Sterling Heights (4) • Clinton Township (1)</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>R19, R20, R21</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Macomb Internal Medicine · Get Well Urgent Care Madison Heights · Ryan Medical Associates · DIAB AND KINNER INTERNAL MEDICINE, PC- use · Michigan Compassionate Care · MI Family Practice · Get Well Urgent Care - Sterling Heights · Schoenherr Parkway Family Practice · Michigan Primary Care - Sterling Heights · Associates in Family Practice</t>
         </is>
       </c>
     </row>
@@ -16428,22 +16841,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>K-R07+R11</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>K-W4D3</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East</t>
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Heights (3) • Beverly Hills (1) • Berkley (1)</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>R10, R20</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Beverly Hills Internal Medicine · Berkley Urgent Care · MICHIGAN PREMIER INTERNISTS · Brigid Healthcare · Team Rehab - SMA Bloomfield Hills · Limitless Physical Therapy and Performance · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Oakland Integrated Healthcare Network</t>
         </is>
       </c>
     </row>
@@ -16458,22 +16893,44 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>K-R12+R13+R22</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>K-W4D4</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>MedPro Primary Care · Oakland Family Practice · Metro Medical Practice · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Farmington Hills (6) • Southfield (3) • Farmington (1)</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>R03, R05</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · Corewell Internal Medicine Southfield · Safir Law · Kajy Law · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150 · Henry Ford Primary Care Center - 160 · Michigan Auto Law · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
         </is>
       </c>
     </row>
@@ -16488,172 +16945,304 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>K-R15+R16+R17</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>K-W4D5</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Westland (3) • Livonia (3) • Canton (2)</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>R02, R08</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>SUNNY PEDIATRICS AND FAMILY · WAYNE MEDICAL CENTER, PLLC · Park Medical Centers · Village Medical - Livonia · Hermann Banks MD PC · PRAVEEN MODI, MD, PC · Plymouth Urgent Care · MHP - West · Village Medical Wayne · Pryde Athletics and Physical Therapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K-W5D1</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic · Swetech Medical Center · MNP · Team Rehabilitation  - Washington · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="E23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Southfield (7) • Farmington Hills (3)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>FAMILY MEDICINE, PC · Carson Center Specialty · Bully Family Physicians · Jian Zu MD · MDVip - Southfield · Ross Law · Berry Johnson Health · Corewell Health Family Medicine - Farmington Hills · Internal Medicine Physicians #170 · Levine Clinic of Chiropractic</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>K-R02+R06+R19</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K-W5D2</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Internal Medicine Physicians #170 · Berry Johnson Health · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine · Hesselberg Chiropractic · Park Medical Centers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="F24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>West Bloomfield (4) • Commerce Township (2) • Commerce Charter Township (1)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>R04, R09</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>IHA UNION LAKE PEDIATRICS · Center For Hollistic Medicine · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · Internal Medicine &amp; Primary Care Specialists- 1010 · Rodnick Chiropractic · DMC Orthopedics - Commerce Township · CoreMed - Commerce · IPHCA · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>K-R03</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K-W5D3</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="F25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Southfield (7) • Bingham Farms (2) • Royal Oak (1)</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>R05, R07</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>DEIGHTON FAMILY PRACTICE - use this one · ROSE MEDICINE · Mark Sisson Law · CHARLES G GODOSHIAN, MD, PC · Wigod &amp; Falzon · Legend Health - Now One Health · Steinberg Law Firm · Ross Gilders Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Applebaum &amp; Stone</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>K-R03+R05+R06</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law · Corwell Health - Farmington</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K-W5D4</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Southfield (3) • West Bloomfield (1) • Farmington (1)</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>R03, R05, R09</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Pavilion Family Practice - use this one · Superior Family Medicine - Health Venters Detroit -use this onea · APH - Pavillion IM Use this one · MARY LEE, MD, PC · Vanstone Injury Law · Corwell Health - Farmington</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>K-R08</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>K-R14+R20</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K-W5D5</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Livonia (6) • Redford (1)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>R08, R15</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Henry Ford Health Medical Center - Seven Mile Road · ARBOR LANE FAMILY PHYSICIANS · Primal Recovery and PT · Brentwood Pediatric Associates · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine</t>
         </is>
       </c>
     </row>
@@ -16668,22 +17257,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>K-R01+R10</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>K-W6D1</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford · SOMERSET PEDIATRICS · Rochester Primary Care</t>
+        <v>6</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Port Huron (6) • Bingham Farms (1) • Marysville (1)</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>R05, R07, R13</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>MEDICAL CENTER PEDIATRICS, PLLC · Port Huron Medicine Associates · Patrick Kut MD PC · Internal Medicine Associates Port Huron · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Lifetime Family Care · SOUTH EAST MICHIGAN MEDICAL ASSOCIATES, PC</t>
         </is>
       </c>
     </row>
@@ -16698,22 +17309,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>K-R04+R08+R20</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>K-W6D2</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>South Lyon Family Docs · Downriver Internists · Elite Family Medicine · Wattles Internal Medicine- use · Primal Recovery and PT · Dr. Robin’s Heath and Wellness Center · iTest Health Family Medicine · Commerce Internal Medicine · Oakland Physicians</t>
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Farmington Hills (3) • Rochester Hills (2) • Troy (1)</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>R04, R09, R10</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>SOMERSET PEDIATRICS · Victor Valentino Law · Rochester Primary Care · Stonebrooke Family Physicians · WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180 · Millenium Associated Physicians - 130A · Commerce Internal Medicine · Oakland Physicians</t>
         </is>
       </c>
     </row>
@@ -16728,22 +17361,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>K-R04+R09</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>K-W6D3</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
+        <v>6</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Warren (7) • Center Line (1) • Roseville (1)</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>R11, R19</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>FERRIS, MARY C, MEDICAL GROUP · Health Care Medical Center · Lupo Chiropractic Center · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · Corewell Health-East · METROPOLITAN MEDICAL ASSOCIATES · Henry Ford Warren Family Physicians · Michigan Adult and Child Medicine · Legacy Family Medicine</t>
         </is>
       </c>
     </row>
@@ -16758,22 +17413,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>K-R05+R07</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>K-W6D4</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Superior Family Medicine - Health Venters Detroit -use this onea · Pavilion Family Practice - use this one · APH - Pavillion IM Use this one · Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · SOUTH EAST MICHIGAN MEDICAL ASSOCIATES, PC · MEDICAL CENTER PEDIATRICS, PLLC</t>
+        <v>5</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Clinton Township (1) • Marysville (1) • Lenox (1)</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>R17, R22</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Swetech Medical Center · Physician HeathCare Network - Marysville · Physician HealthCare Network · Henry Ford Medical Center - East Jefferson · Cornerstone Lakefront Internists · Team Rehabilitation  - Washington · Silver Pine Medical Group - Sterling Heights · Cornerstone St. Clair Internists · Souva PT and Performance · MNP</t>
         </is>
       </c>
     </row>
@@ -16788,172 +17465,304 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>K-R10</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>K-W6D5</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians</t>
+      <c r="F32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Grosse Pointe (4) • Hamtramck (2) • Detroit (1)</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>FAMILY CARE CENTER OF HAMTRAMCK, PC · Hamtramck Community Medical Center · Marko Law · GROSSE POINTE PARK INTERNAL MEDICINE CENTER · Grosse Pointe Physicians and Surgeons · Jefferson Family Practice (Cornerstone) · Henry Ford Main Internal Medicine - Grosse Pointe</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>K-R02</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Pryde Athletics and Physical Therapy · SUNNY PEDIATRICS AND FAMILY · Plymouth Urgent Care · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · WAYNE MEDICAL CENTER, PLLC</t>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>K-W7D1</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Warren (8) • Sterling Heights (2)</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>R12, R19</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Pioneer Medical Associates - Warren · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Ryan Medical Associates · Sterling Family Medicine · DIAB AND KINNER INTERNAL MEDICINE, PC- use · Michigan Compassionate Care · MI Family Practice · Get Well Urgent Care - Sterling Heights · Plumbrook Medical Center</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>K-R03+R18+R19</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>K-W7D2</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights · Henry Ford Main Internal Medicine - Grosse Pointe · Jefferson Family Practice (Cornerstone) · FAMILY CARE CENTER OF HAMTRAMCK, PC · Henry Ford Internal &amp; Family Medicine - Farmington Hills -170 · Henry Ford Internists - Farmington Hills 150</t>
+      <c r="E34" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Sterling Heights (4) • Troy (2) • Madison Heights (1)</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Get Well Urgent Care Madison Heights · Berkley Urgent Care · Brigid Healthcare · Wattles Internal Medicine- use · South Lyon Family Docs · Downriver Internists · Elite Family Medicine · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>K-R06+R11</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>K-W7D3</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Health Family Medicine - Farmington Hills · Bully Family Physicians · MDVip - Southfield · FAMILY MEDICINE, PC · Lupo Chiropractic Center · Henry Ford Warren Family Physicians · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · FERRIS, MARY C, MEDICAL GROUP · Corewell Health-East</t>
+      <c r="E35" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Southfield (2) • Livonia (2) • Farmington (2)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>R01, R02</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Christensen Law · Mike Morse Law Firm · Park Medical Centers · Triumph chiropractic · Hesselberg Chiropractic · Beaumont Medical Center - Redford · SHEIKH MEDICAL CENTER · Village Medical Farmington · Legacy Family Care · Powers Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>K-R12+R13+R22</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>K-W7D4</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>MedPro Primary Care · Oakland Family Practice · Metro Medical Practice · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Port Huron Medicine Associates · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
+      <c r="E36" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Fort Gratiot (2) • Port Huron (2) • Yale (2)</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Lake Huron Medical Center - Fort Gratiot · McLaren Port Huron Fort Gratiot Internal Medicine · Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Blue Water Urgent Care - Port Huron · Dr. Carley and Associates · Wadhams Family Care · Yale Family Care · Yale Community Heath Center - VA Clinic · Croswell Clinic - McKenzie Health System · Lexington Family Medicine</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>K-R15+R16+R17</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Producer sweep</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>K-W7D5</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Physician HealthCare Network Urgent Care and Walk In- Fort Gratiot · Lexington Family Medicine · Yale Family Care · Yale Community Heath Center - VA Clinic · Swetech Medical Center · MNP · Team Rehabilitation  - Washington · ARBOR LANE FAMILY PHYSICIANS · GARDEN CITY FAMILY PHYSICIANS · Greg Monroe DO PC</t>
+      <c r="E37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Sterling Heights (6) • Clinton Township (2) • Macomb Township (1)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Beaumont Family Medicine - Sterling Heights · Macomb Internal Medicine · David S Weingarden MD &amp; Associates · Office of David Mandy DO · Academic Internal Medicine (Ascension) · Toma &amp; Yaldo Medical Center · Sterling Heights Urgent Care · Schoenherr Parkway Family Practice · Michigan Primary Care - Sterling Heights · Associates in Family Practice</t>
         </is>
       </c>
     </row>
@@ -16968,22 +17777,44 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>K-R01+R02+R08</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>K-W8D1</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Hesselberg Chiropractic · Park Medical Centers · Hermann Banks MD PC · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · Brentwood Pediatric Associates · Village Medical - Livonia · Henry Ford Health Medical Center - Seven Mile Road · Corewell Health Farmington Hills Hospital Family Medicine · Henry Ford Health - Family Medicine 8 Mile Livonia</t>
+        <v>5</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Novi (4) • Farmington Hills (3) • Northville (2)</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>R03, R14</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>TONI BALLITCH TRATE, DO, PC · Providence Park Pediatrics - Novi · WELL BEING PEDIATRICS · Trinity IHA Primary Care - Schoolcraft Campus · Medical Clinic of Northville · Village Medical - Northville West · Haller and Hug Internal Medicine · Michigan Auto Law · ASCENSION MEDICAL GROUP PROVIDENCE FAMILY AND ATHLETIC MEDICINE · Ivy Rehab - Novi</t>
         </is>
       </c>
     </row>
@@ -16998,22 +17829,44 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>K-R03+R04</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>K-W8D2</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Corewell Internal Medicine Southfield · Safir Law · Henry Ford Primary Care Center - 160 · Michigan Auto Law · FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · ORCHARD PRIMARY CARE · Ivy Rehab - Farmington · IPHCA · Internal Medicine &amp; Primary Care Specialists- 1010</t>
+        <v>4</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Westland (3) • Allen Park (2) • Garden City (2)</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>R08, R15</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>ARBOR LANE FAMILY PHYSICIANS · BEAUMONT FAMILY MEDICINE WESTLAND · ALLEN PARK FAMILY PHYSICIANS · Corewell Urgent Care - Allen Park · Premier Pediatrics Dearborn Heights · GARDEN CITY FAMILY PHYSICIANS · Corewell Health Urgent Care - Garden City · Hermann Banks MD PC · WESTLAND CLINIC - use · Greg Monroe DO PC</t>
         </is>
       </c>
     </row>
@@ -17028,22 +17881,44 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>K-R05+R06</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>K-W8D3</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Lifetime Family Care · Ross Gilders Law · DEIGHTON FAMILY PRACTICE - use this one · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC · Corewell Urgent Care - Royal Oak · Levine Clinic of Chiropractic · Jian Zu MD · Carson Center Specialty · Ross Law</t>
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Southfield (3) • Port Huron (2) • Royal Oak (2)</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>R05, R13, R17</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>DEIGHTON FAMILY PRACTICE - use this one · Macomb Spine Care · Henry Ford Orthopedics &amp; Sports Medicine - Chesterfield · Blue Water Internal Medicine PC · Physician HeathCare Network - Michele Raymond DO · Corewell Urgent Care - Royal Oak · Ross Gilders Law · Kajy Law · SOUTHFIELD MEDICAL CLINIC AND PREMIER URGENT CARE AND WALK IN CLINIC</t>
         </is>
       </c>
     </row>
@@ -17058,22 +17933,44 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>K-R07+R20</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>K-W8D4</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>CHARLES G GODOSHIAN, MD, PC · Legend Health - Now One Health · Mark Sisson Law · Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare</t>
+        <v>3</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Sterling Heights (3) • Troy (2) • Warren (2)</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>R12, R22</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>MedPro Primary Care · Waypointe Internal Medicine · Metro Medical Practice · Roseville Family Practice · Oakland Family Practice · Troy Internal Medicine · Neil King Physical Therapy · Purdy Chiropractic Center · Sterling Medical Center &amp; Urgent Care · BASEL BRIKHO MEDICAL GROUP - use this one</t>
         </is>
       </c>
     </row>
@@ -17088,179 +17985,358 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>K-R09+R10</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>K-W8D5</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Livonia (4) • Westland (3) • Canton (2)</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>R02, R08</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>SUNNY PEDIATRICS AND FAMILY · Henry Ford Health Medical Center - Seven Mile Road · WAYNE MEDICAL CENTER, PLLC · Brentwood Pediatric Associates · Village Medical - Livonia · AGHA INTERNAL MEDICINE AND ASSOCIATES, PC · PRAVEEN MODI, MD, PC · MHP - West · Village Medical Wayne · Pryde Athletics and Physical Therapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>K-W9D1</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>St. Clair Shores (3) • Roseville (2) • Clinton Township (1)</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>R17, R22</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>Swetech Medical Center · MyCare Health Center - Mt Clemens · Aquino Integrative Internal Medicine · Allied Internists · Henry Ford Medical Center - East Jefferson · Cornerstone Lakefront Internists · Epic Health - St Clair Shores · Masonic Medical Center - Ascension · Team Rehabilitation  - Washington · MNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>K-W9D2</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>West Bloomfield (4) • Farmington Hills (2) • Southfield (1)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>R03, R09</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>FARMINGTON HILLS  FAMILY PHYSICIANS, PLLC · Center For Hollistic Medicine · Associates in Internal Medicine - MHP · Safir Law · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · MARY LEE, MD, PC · Internal Medicine Specialists · Vanstone Injury Law · Henry Ford Primary Care Center - 160 · Ivy Rehab - Farmington</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>K-W9D3</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Warren (5) • Southfield (3) • Roseville (1)</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>R05, R11</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>FERRIS, MARY C, MEDICAL GROUP · Lupo Chiropractic Center · Lifetime Family Care · Pavilion Family Practice - use this one · Superior Family Medicine - Health Venters Detroit -use this onea · APH - Pavillion IM Use this one · Northpointe Pediatrics · Pulmonary &amp; Medical Associates · Corewell Health-East · Henry Ford Warren Family Physicians</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>K-W9D4</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>WEST BLOOMFIELD INTERNAL MEDICINE, PLLC · Millenium Associated Physicians - 130A · Millennium Affiliated Physicians - 130B · Premier Internists - Suite 180 · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Team Rehab - SMA Bloomfield Hills · Oakland Integrated Healthcare Network · Limitless Physical Therapy and Performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="F46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Port Huron (5) • Southfield (3) • Farmington Hills (2)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>R06, R13</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>Port Huron Medicine Associates · Carson Center Specialty · Jian Zu MD · Ross Law · John Mullally MD PC · Michigan Neurology and Spine Center · Mitchell Medical Center · Huron Family Practice Center · Corewell Health Family Medicine - Farmington Hills · Levine Clinic of Chiropractic</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>K-R01</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Mike Morse Law Firm · Christensen Law · Legacy Family Care · Powers Family Medicine · Village Medical Farmington · SHEIKH MEDICAL CENTER · Triumph chiropractic · Beaumont Medical Center - Redford</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>K-R04+R09</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>K-W9D5</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>DMC Orthopedics - Commerce Township · CoreMed - Commerce · IHA UNION LAKE PEDIATRICS · Rodnick Chiropractic · PILLAY INTERNAL MEDICINE ASSOCIATES, PLLC · DMC PRIMARY AND SPECIALTY CARE WEST BLOOMFIELD · HENRY FORD MEDICAL CENTER FARMINGTON ROAD INTERNAL MEDICINE · Center For Hollistic Medicine · MARY LEE, MD, PC · Vanstone Injury Law</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>K-R07+R09+R19</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Applebaum &amp; Stone · Wigod &amp; Falzon · Steinberg Law Firm · ROSE MEDICINE · Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine · Internal Medicine Specialists · Associates in Internal Medicine - MHP</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>K-R10+R14</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Victor Valentino Law · TWIN LAKES MEDICAL ASSOCIATES, PC · Stonebrooke Family Physicians · TONI BALLITCH TRATE, DO, PC · Medical Clinic of Northville · Village Medical - Northville West · Providence Park Pediatrics - Novi</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>K-R21</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>First pass</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Toma &amp; Yaldo Medical Center · Michigan Primary Care - Sterling Heights · Beaumont Family Medicine - Sterling Heights · Associates in Family Practice · Sterling Heights Urgent Care · Schoenherr Parkway Family Practice · Macomb Internal Medicine · David S Weingarden MD &amp; Associates · Office of David Mandy DO · Academic Internal Medicine (Ascension)</t>
+      <c r="E47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Grosse Pointe (2) • Farmington Hills (1) • Beverly Hills (1)</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>R01, R02, R10, R18</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>Open in Maps</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Corewell Health Farmington Hills Hospital Family Medicine · Beverly Hills Internal Medicine · MICHIGAN PREMIER INTERNISTS · Henry Ford Health - Family Medicine 8 Mile Livonia · Plymouth Urgent Care · FAMILY CARE CENTER OF HAMTRAMCK, PC · Jefferson Family Practice (Cornerstone) · Henry Ford Main Internal Medicine - Grosse Pointe · TWIN LAKES MEDICAL ASSOCIATES, PC · Oakland Integrated Healthcare Network</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17328,177 +18404,177 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>1235164872</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Kids First Pediatrics</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Other / Verify</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Hazel Park</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>c53a52e1-de9e-438f-87b9-f80c5bf3c183</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>NICOLOFF HOLISTIC FAMILY MEDICINE</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>LIVONIA</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>holistic med - doesn't see reps</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>377517aa-6082-4575-9083-498d5aca7ecb</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>GAMMONS MEDICAL</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>PCP</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>WARREN</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr"/>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>57c8b393-1204-4def-8cf0-5461a39e5e14</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Blue Water Urgent Care</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Urgent Care</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Marysville</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>95% Medicaid</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>b5b7ec36-68c2-4b3f-b1bc-7efada3e145f</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Metropolitan Orthopedic Associates</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Orthopedic</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Grosse Pointe</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Tagged “Non-Spine” group via MMC import — out of spine rotation</t>
         </is>
